--- a/nr-doc-core-service-request/ig/CodeSystem-fr-core-cs-champ-activite.xlsx
+++ b/nr-doc-core-service-request/ig/CodeSystem-fr-core-cs-champ-activite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T14:55:35+00:00</t>
+    <t>2026-09-16T07:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/CodeSystem-fr-core-cs-champ-activite.xlsx
+++ b/nr-doc-core-service-request/ig/CodeSystem-fr-core-cs-champ-activite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T07:37:42+00:00</t>
+    <t>2026-09-17T12:36:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/CodeSystem-fr-core-cs-champ-activite.xlsx
+++ b/nr-doc-core-service-request/ig/CodeSystem-fr-core-cs-champ-activite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:36:37+00:00</t>
+    <t>2026-09-17T13:03:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/nr-doc-core-service-request/ig/CodeSystem-fr-core-cs-champ-activite.xlsx
+++ b/nr-doc-core-service-request/ig/CodeSystem-fr-core-cs-champ-activite.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T13:03:48+00:00</t>
+    <t>2026-10-13T08:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
